--- a/docs/teaching/2026-春季/汽服2302B班/docs/汽服2302B班_2026春季学期成绩册_updated_20260610_010822.xlsx
+++ b/docs/teaching/2026-春季/汽服2302B班/docs/汽服2302B班_2026春季学期成绩册_updated_20260610_010822.xlsx
@@ -1455,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J9" s="6" t="n">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>原创</t>
+          <t>未完成</t>
         </is>
       </c>
       <c r="J13" s="6" t="n">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J25" s="6" t="n">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="G30" s="8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J34" s="10" t="n">
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>抄袭</t>
+          <t>原创</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
@@ -3584,6 +3584,62 @@
       </c>
       <c r="O39" s="6" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>23071140205</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>任梦泱</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>23071140209</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>次美业</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
       </c>
     </row>
   </sheetData>
